--- a/hypotheses/tables/hypotheses.xlsx
+++ b/hypotheses/tables/hypotheses.xlsx
@@ -16,8 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+  </numFmts>
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,13 +27,21 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DDDDDD"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -46,8 +56,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,13 +432,864 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:Z6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="50" customWidth="1" min="15" max="15"/>
+    <col width="50" customWidth="1" min="16" max="16"/>
+    <col width="50" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="50" customWidth="1" min="20" max="20"/>
+    <col width="50" customWidth="1" min="21" max="21"/>
+    <col width="16" customWidth="1" min="22" max="22"/>
+    <col width="50" customWidth="1" min="23" max="23"/>
+    <col width="50" customWidth="1" min="24" max="24"/>
+    <col width="50" customWidth="1" min="25" max="25"/>
+    <col width="50" customWidth="1" min="26" max="26"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>No hypotheses yet</t>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>slug</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>_status_dir</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>lifecycle</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>owner</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>created</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>updated</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>fpf_F</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>fpf_G</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>fpf_R</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>strategic_region</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>test_method</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>success_criteria</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>refutation_criteria</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>outcome</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>learning_extracted</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>alphas</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>linked_artefacts</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>linked_hypotheses</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>_file</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>cross_cite</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>resources_needed</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>test_scope</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>H-001</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Meta-method (cycle + discipline + output + reflection) applicable cross-domain beyond engineering</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>meta-method-success-formula-applicable-cross-domain</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>samples</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>method</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>ruslan</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="n">
+        <v>46162</v>
+      </c>
+      <c r="J2" s="3" t="n">
+        <v>46162</v>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>F3</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>jetix-foundation</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>catallactic</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Применить meta-method (паттерн «cycle defined → discipline → output → reflection»)
+к 3 non-engineering доменам:
+  1. Education domain — построить mini-cycle обучения новому навыку
+  2. Personal-dev domain — построить mini-cycle daily habit
+  3. Pitch development domain — построить mini-cycle iterations of pitch
+Каждый domain получает clean cycle execution + reflection write-up.
+</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">- Each of 3 domains has working cycle (≥1 full iteration)
+- Reflection write-up identifies common pattern across all 3
+- Pattern matches «cycle defined → discipline → output → reflection» structure
+- Compound learning extracted (1-3 lines per domain)
+</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">- Pattern fails в ≥2 of 3 domains (cycle breaks; output absent; no reflection possible)
+- Common structure не identifiable across domains
+- Forced fitting required → likely overgeneralization
+</t>
+        </is>
+      </c>
+      <c r="R2" s="2" t="inlineStr"/>
+      <c r="S2" s="2" t="inlineStr"/>
+      <c r="T2" s="2" t="inlineStr">
+        <is>
+          <t>[{alpha: way-of-working, state: foundation_established}, {alpha: work, state: prepared}]</t>
+        </is>
+      </c>
+      <c r="U2" s="2" t="inlineStr">
+        <is>
+          <t>[wiki/concepts/method-systems-thinking.md, research/levenchuk-books-distillation-2026-05-20/06-cross-link-к-jetix-substrate.md]</t>
+        </is>
+      </c>
+      <c r="V2" s="2" t="inlineStr">
+        <is>
+          <t>[H-005]</t>
+        </is>
+      </c>
+      <c r="W2" s="2" t="inlineStr">
+        <is>
+          <t>hypotheses/samples/H-001-meta-method-success-formula-applicable-cross-domain.md</t>
+        </is>
+      </c>
+      <c r="X2" s="2" t="inlineStr">
+        <is>
+          <t>Левенчук Методология 2025 Гл. 4 (MG4 ⭐⭐⭐): «метод как объект 1-го класса +
+alpha-machinery» — meta-method tracking infrastructure. Этот тест проверяет
+whether meta-method itself generalizes как primitive.
+Также: wiki/concepts/method-systems-thinking.md §APPEND batch-8 — initial substrate.</t>
+        </is>
+      </c>
+      <c r="Y2" s="2" t="inlineStr">
+        <is>
+          <t>[{estimate: 60-90h spread across 3 domains, resource: R2-time}, {estimate: Левенчук
+      Методология Гл. 4 + meta-method substrate, resource: R5-knowledge}]</t>
+        </is>
+      </c>
+      <c r="Z2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Generalization across 3 non-engineering domains. NOT testing universal applicability
+(5+ domain test would require). Bounded к catallactic-region domains.
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>H-002</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Partnership-frame outperforms cheat-code positioning для L2 outreach</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>partnership-frame-better-than-cheatcode-l2</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>samples</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>outreach</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>ruslan</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="n">
+        <v>46162</v>
+      </c>
+      <c r="J3" s="3" t="n">
+        <v>46162</v>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>F2</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>outreach-pipeline</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>catallactic</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A/B test outreach messages к L2 founders/operators:
+  - Frame A («cheat-code»): «I have an AI methodology that gives you cheat-code shortcut»
+  - Frame B («partnership»): «I'd like to explore a co-creation partnership на methodology X»
+Кооперативный split: 10 outreach к sample, 5 каждым frame.
+Measure: reply rate + reply quality (interest level) + meeting conversion.
+</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">- Frame B reply rate ≥2× Frame A
+- Frame B meeting conversion ≥2× Frame A
+- Qualitative: Frame B replies show higher engagement (longer, more questions)
+</t>
+        </is>
+      </c>
+      <c r="Q3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">- Frame A wins on reply rate AND meeting conversion (positioning intuition wrong)
+- No significant difference (n too small OR confounds dominate)
+- Frame B triggers «scammy» pushback (over-claim risk)
+</t>
+        </is>
+      </c>
+      <c r="R3" s="2" t="inlineStr"/>
+      <c r="S3" s="2" t="inlineStr"/>
+      <c r="T3" s="2" t="inlineStr">
+        <is>
+          <t>[{alpha: stakeholder, state: recognized}, {alpha: opportunity, state: identified}]</t>
+        </is>
+      </c>
+      <c r="U3" s="2" t="inlineStr">
+        <is>
+          <t>[wiki/concepts/pre-existing-partnership-positioning.md, decisions/REFLECTION-INBOX-2026-05-16.md]</t>
+        </is>
+      </c>
+      <c r="V3" s="2" t="inlineStr">
+        <is>
+          <t>[H-005]</t>
+        </is>
+      </c>
+      <c r="W3" s="2" t="inlineStr">
+        <is>
+          <t>hypotheses/samples/H-002-partnership-frame-better-than-cheatcode-l2.md</t>
+        </is>
+      </c>
+      <c r="X3" s="2" t="inlineStr">
+        <is>
+          <t>wiki/concepts/pre-existing-partnership-positioning.md — substrate concept ack F2.
+Связано с broader thesis: «не cheat-code; не consulting; partnership с pre-existing artefact».</t>
+        </is>
+      </c>
+      <c r="Y3" s="2" t="inlineStr">
+        <is>
+          <t>[{estimate: 20-30h outreach + 10h drafts, resource: R2-time}, {estimate: medium —
+      пара intros from existing network, resource: R4-trust}]</t>
+        </is>
+      </c>
+      <c r="Z3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L2 founders/operators ≥1 year operating; with existing org infrastructure.
+NOT testing: L1 (different dynamics); cold ICPs (require warmer entry).
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>H-003</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>3-tier funnel (Tier-1 entry workshop → Tier-2 cohort → Tier-3 partner) 3-6 month lifecycle optimal</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>3tier-funnel-3to6-months-optimal</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>samples</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>business</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>ruslan</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>46162</v>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>46162</v>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>F2</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>jetix-business-model</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>catallactic</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Сконфигурировать 3-tier funnel и запустить 1 cycle:
+  - Tier 1: Engineer Entry Workshop (1-day; €99) — broad funnel entry
+  - Tier 2: Cohort program (4-8 weeks; €499) — deep dive с группой
+  - Tier 3: Partner program (3-6 months; €5000+) — 1-1 methodology co-creation
+Cycle ≥3 месяца для observable conversion.
+Measure: T1→T2 conversion %, T2→T3 conversion %, retention, NPS.
+</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">- T1→T2 conversion ≥10% (commonly accepted SaaS-cohort benchmark scaled)
+- T2→T3 conversion ≥20% (deeper-funnel typically higher %)
+- NPS ≥30 at T1 close (would-recommend signal)
+- Unit economics positive at end of cycle (no subsidization)
+</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">- T1→T2 conversion &lt;5% (broad funnel doesn't qualify)
+- T2→T3 conversion &lt;10% (cohort doesn't translate к partner)
+- Negative NPS (rejection signal)
+- Unit economics negative beyond first cycle
+</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr"/>
+      <c r="S4" s="2" t="inlineStr"/>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>[{alpha: opportunity, state: solution_needed}, {alpha: requirements, state: bounded},
+  {alpha: stakeholder, state: recognized}]</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>[wiki/concepts/project-of-humanity-positioning.md, reports/sprint-synthesis-v2-2026-05-19-evening/04-master-packaging-step6-roadmap.md,
+  daily-logs/_EXECUTION-PLAN-FINAL-2026-05-20-evening.md]</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>[H-002]</t>
+        </is>
+      </c>
+      <c r="W4" s="2" t="inlineStr">
+        <is>
+          <t>hypotheses/samples/H-003-3tier-funnel-3to6-months-optimal.md</t>
+        </is>
+      </c>
+      <c r="X4" s="2" t="inlineStr">
+        <is>
+          <t>Platform v2 §3 32-resource framework + 15 monetization variants — substrate substrate.
+Связано с BL-1 Engineer Workshop ack (19.05 evening Top-5).</t>
+        </is>
+      </c>
+      <c r="Y4" s="2" t="inlineStr">
+        <is>
+          <t>[{estimate: 200-300h за 3-6 мес cycle, resource: R2-time}, {estimate: &lt;€2000 marketing,
+    resource: R1-money}, {estimate: Platform v2 §3 32-resources + Левенчук методология,
+    resource: R5-knowledge}]</t>
+        </is>
+      </c>
+      <c r="Z4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Single 3-6 month cycle; sample size: ≥30 T1 entries, ≥5 T2 cohort, 1-2 T3 partners.
+NOT testing: 12-month sustainability (would need separate cycle).
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>H-004</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Imagination as 13th component of intellect-stack (extension к Левенчук 12-component model)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>imagination-as-intellect-component</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>samples</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>method</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>ruslan</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="n">
+        <v>46162</v>
+      </c>
+      <c r="J5" s="3" t="n">
+        <v>46162</v>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>F2</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>intellect-stack</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Литературно-критический + empirical hybrid:
+  1. Прочитать Левенчук Интеллект-стек 2023 целиком; map 12 components Левенчук
+  2. Audit моего собственного reasoning workflows за 2 недели — surface where
+     «imagination» distinctly appears (vs other 12 components)
+  3. Если distinct → draft 1-page argument с 5-7 concrete examples
+  4. Cross-check с philosophical / cognitive science sources (Tversky / Penrose / etc.)
+  5. Optional: send draft к philosophy-expert agent для critique
+</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">- 5-7 concrete examples где imagination distinctly required (не reducible к other 12)
+- Survives philosophy-expert critique (≥3 of 5 reasoning passes)
+- Clear differentiating definition from creativity / fantasy / generation
+- Optional: F4 promotion с Левенчук cross-review
+</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">- Imagination reducible к existing 12 components (e.g., always = «model-fragment manipulation» + «hypothesis generation»)
+- Cannot define distinctly without circular reference
+- Philosophy critique rejects ≥3 of 5 examples
+</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr"/>
+      <c r="S5" s="2" t="inlineStr"/>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>[{alpha: requirements, state: conceived}, {alpha: way-of-working, state: principles_established}]</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>[daily-logs/_HYPOTHESIS-TABLES-DECISION-2026-05-20.md]</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="W5" s="2" t="inlineStr">
+        <is>
+          <t>hypotheses/samples/H-004-imagination-as-intellect-component.md</t>
+        </is>
+      </c>
+      <c r="X5" s="2" t="inlineStr">
+        <is>
+          <t>Левенчук Интеллект-стек 2023 — 12 functional skills as primary substrate
+K-4 Intellect-12-Component Audit (previous Jetix Tier B research) — informs gap analysis
+daily-logs/_HYPOTHESIS-TABLES-DECISION-2026-05-20.md (where surfaced)</t>
+        </is>
+      </c>
+      <c r="Y5" s="2" t="inlineStr">
+        <is>
+          <t>[{estimate: 20-40h reading + 10-20h drafting, resource: R2-time}, {estimate: Левенчук
+      Intellect-stack 2023 + cognitive science basics, resource: R5-knowledge}, {
+    estimate: high — потенциально пишет в FPF↔СМ exchange, resource: R4-trust}]</t>
+        </is>
+      </c>
+      <c r="Z5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Intellect-stack scope как defined by Левенчук 2023; NOT extending к general AI
+cognitive architecture. Bounded к humanly-relevant intellect components.
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>H-005</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Method as 1st-class object enables recursive self-improvement engine (per Левенчук MG4 + Jetix substrate)</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>method-as-1st-class-object-recursive-engine</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>samples</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>method</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>ruslan</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>46162</v>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>46162</v>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>F3</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>jetix-foundation</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>catallactic</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Existing Jetix substrate уже demonstrates pattern. Test = explicit corroboration:
+  1. Document 3 instances где method-as-1st-class-object enabled recursive improvement:
+     a. Hypothesis substrate itself (recursive — substrate has way-of-working alpha tracking its own maturity)
+     b. FPF lens application к itself (FPF developed using FPF discipline)
+     c. Левенчук distillation method = also recursive (method = its own object)
+  2. Cross-check с Методология 2025 Гл. 4 MG4 предписаниями
+  3. Validate с audio_703 (existing voice memo containing recursive engine framing)
+  4. Validate с wiki/concepts/recursive-supportive-control-pattern.md
+</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">- 3 instances documented с clear method-object distinction
+- Each instance shows compound improvement (method N → method N+1)
+- Compatible с Методология 2025 Гл. 4 MG4 specifications
+- audio_703 + recursive-supportive-control-pattern cross-validate
+</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">- Pattern не distinct от «iteration» или «refactoring» (not 1st-class object claim)
+- Метод changes are caused by external triggers, не recursive self-application
+- Audio + wiki pattern divergent от Методология MG4
+</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr"/>
+      <c r="S6" s="2" t="inlineStr"/>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>[{alpha: way-of-working, state: foundation_established}, {alpha: software-system,
+    state: demonstrable}, {alpha: work, state: under_control}]</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>[wiki/concepts/method-systems-thinking.md, wiki/concepts/recursive-supportive-control-pattern.md,
+  research/levenchuk-books-distillation-2026-05-20/06-cross-link-к-jetix-substrate.md]</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>[H-001, H-003]</t>
+        </is>
+      </c>
+      <c r="W6" s="2" t="inlineStr">
+        <is>
+          <t>hypotheses/samples/H-005-method-as-1st-class-object-recursive-engine.md</t>
+        </is>
+      </c>
+      <c r="X6" s="2" t="inlineStr">
+        <is>
+          <t>**Primary:** Левенчук Методология 2025 Гл. 4 MG4 ⭐⭐⭐ — «метод как объект 1-го класса».
+**Substrate:** wiki/concepts/method-systems-thinking.md §APPEND batch-8 + audio_703 reference.
+**Pattern:** wiki/concepts/recursive-supportive-control-pattern.md — related broader pattern.
+**Distillation:** research/levenchuk-books-distillation-2026-05-20/06-cross-link-к-jetix-substrate.md §2.1.</t>
+        </is>
+      </c>
+      <c r="Y6" s="2" t="inlineStr">
+        <is>
+          <t>[{estimate: ongoing — substrate уже under_control; новые apps incremental, resource: R2-time},
+  {estimate: Левенчук Методология 2025 Гл. 4 + Jetix substrate own dogfooding, resource: R5-knowledge}]</t>
+        </is>
+      </c>
+      <c r="Z6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jetix Foundation scope — testing pattern в Jetix substrate own dogfooding.
+NOT testing universal applicability (would need cross-domain replication = H-001's territory).
+</t>
         </is>
       </c>
     </row>
